--- a/Income & Cost Spreadsheet.xlsx
+++ b/Income & Cost Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/nathan_davis2_westpoint_edu/Documents/Documents/MY OWN WEBSITE!!!/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1213" documentId="8_{6087132D-B281-4ECA-AD9E-C22E4686363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A037D7BE-DE47-4195-95EB-CB951028BF79}"/>
+  <xr:revisionPtr revIDLastSave="1214" documentId="8_{6087132D-B281-4ECA-AD9E-C22E4686363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30A0D911-D74C-4AFD-B9F6-132A31FAD224}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5016BA3E-3704-452A-B527-6130FB509E87}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="76">
   <si>
     <t>Expenses</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>PAYCHECK 2</t>
+  </si>
+  <si>
+    <t>Hello!</t>
   </si>
 </sst>
 </file>
@@ -704,7 +707,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -738,15 +741,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -785,7 +779,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -810,24 +803,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -844,7 +819,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -854,20 +828,40 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -883,50 +877,18 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
+        <right/>
+        <top style="thin">
           <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -952,21 +914,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -977,9 +924,6 @@
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1024,13 +968,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1044,6 +981,42 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1066,14 +1039,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{44CDD88F-02C6-4D42-809D-98045D571AF7}" name="FinanceData" displayName="FinanceData" ref="A2:E51" totalsRowShown="0" headerRowDxfId="6" dataDxfId="10" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{44CDD88F-02C6-4D42-809D-98045D571AF7}" name="FinanceData" displayName="FinanceData" ref="A2:E51" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A2:E51" xr:uid="{44CDD88F-02C6-4D42-809D-98045D571AF7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{85BCECAD-3C8F-462D-B514-B758E78941CC}" name="Month" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{B2B0ABB5-0019-4ED9-BE43-219C89CFFEB2}" name="Category" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{53A39C36-651D-4F16-BDDD-F18CC9207A04}" name="Subcategory" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{DD3B0342-4844-45F1-B4DD-4DFF5870AD43}" name="Description" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{01769327-8652-4DAF-8E46-1B4F9C8FBA9D}" name="COST (Enter manually here)" dataDxfId="8" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{85BCECAD-3C8F-462D-B514-B758E78941CC}" name="Month" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B2B0ABB5-0019-4ED9-BE43-219C89CFFEB2}" name="Category" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{53A39C36-651D-4F16-BDDD-F18CC9207A04}" name="Subcategory" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{DD3B0342-4844-45F1-B4DD-4DFF5870AD43}" name="Description" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{01769327-8652-4DAF-8E46-1B4F9C8FBA9D}" name="COST (Enter manually here)" dataDxfId="2" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1445,29 +1418,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="67"/>
-      <c r="F1" s="65" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="F1" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="67"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
-      <c r="F2" s="21" t="s">
+      <c r="C2" s="58"/>
+      <c r="D2" s="59"/>
+      <c r="F2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-      <c r="J2" s="64" t="s">
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
+      <c r="J2" s="53" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1593,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="19" t="e">
-        <f>C8/$C$5*100</f>
+        <f t="shared" ref="D8:D17" si="0">C8/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F8" s="17" t="s">
@@ -1604,13 +1577,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="19" t="e">
-        <f>G8/$C$5*100</f>
+        <f t="shared" ref="H8:H17" si="1">G8/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
-      <c r="J8" s="63" t="s">
+      <c r="J8" s="52" t="s">
         <v>70</v>
       </c>
       <c r="K8" t="s">
@@ -1626,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="e">
-        <f>C9/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F9" s="17" t="s">
@@ -1637,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="19" t="e">
-        <f>G9/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I9">
@@ -1659,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="19" t="e">
-        <f>C10/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F10" s="17" t="s">
@@ -1670,11 +1643,14 @@
         <v>0</v>
       </c>
       <c r="H10" s="19" t="e">
-        <f>G10/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I10">
         <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
@@ -1686,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="19" t="e">
-        <f>C11/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F11" s="17" t="s">
@@ -1697,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="19" t="e">
-        <f>G11/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I11">
@@ -1713,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="19" t="e">
-        <f>C12/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F12" s="17" t="s">
@@ -1724,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="19" t="e">
-        <f>G12/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I12">
@@ -1740,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="19" t="e">
-        <f>C13/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F13" s="17" t="s">
@@ -1751,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="19" t="e">
-        <f>G13/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I13">
@@ -1767,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="19" t="e">
-        <f>C14/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F14" s="17" t="s">
@@ -1778,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="19" t="e">
-        <f>G14/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I14">
@@ -1794,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="19" t="e">
-        <f>C15/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F15" s="17" t="s">
@@ -1805,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="19" t="e">
-        <f>G15/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I15">
@@ -1821,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="19" t="e">
-        <f>C16/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F16" s="17" t="s">
@@ -1832,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="19" t="e">
-        <f>G16/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I16">
@@ -1848,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="19" t="e">
-        <f>C17/$C$5*100</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F17" s="17" t="s">
@@ -1859,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="19" t="e">
-        <f>G17/$C$5*100</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I17">
@@ -1870,7 +1846,7 @@
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="24"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="20" t="e">
         <f>#REF!/$C$5*100</f>
         <v>#REF!</v>
@@ -1878,7 +1854,7 @@
       <c r="F18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="24"/>
+      <c r="G18" s="21"/>
       <c r="H18" s="20" t="e">
         <f>#REF!/$C$5*100</f>
         <v>#REF!</v>
@@ -1923,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="19" t="e">
-        <f t="shared" ref="D20:D33" si="0">C20/$C$5*100</f>
+        <f t="shared" ref="D20:D33" si="2">C20/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F20" s="17" t="s">
@@ -1934,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="19" t="e">
-        <f t="shared" ref="H20:H33" si="1">G20/$C$5*100</f>
+        <f t="shared" ref="H20:H33" si="3">G20/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I20">
@@ -1950,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F21" s="17" t="s">
@@ -1961,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1974,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F22" s="17" t="s">
@@ -1985,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1998,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F23" s="17" t="s">
@@ -2009,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2017,17 +1993,17 @@
       <c r="B24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="24"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="20" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="24"/>
+      <c r="G24" s="21"/>
       <c r="H24" s="20" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2040,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F25" s="17" t="s">
@@ -2051,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2064,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F26" s="17" t="s">
@@ -2075,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2107,17 +2083,17 @@
       <c r="B28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="24"/>
+      <c r="C28" s="21"/>
       <c r="D28" s="20" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="24"/>
+      <c r="G28" s="21"/>
       <c r="H28" s="20" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2130,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F29" s="17" t="s">
@@ -2141,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2154,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F30" s="17" t="s">
@@ -2165,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2178,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F31" s="17" t="s">
@@ -2189,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2202,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F32" s="17" t="s">
@@ -2213,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="19" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2225,8 +2201,8 @@
         <f>SUM(C8:C31)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="25" t="e">
-        <f t="shared" si="0"/>
+      <c r="D33" s="22" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F33" s="9" t="s">
@@ -2236,8 +2212,8 @@
         <f>SUM(G8:G31)</f>
         <v>0</v>
       </c>
-      <c r="H33" s="25" t="e">
-        <f t="shared" si="1"/>
+      <c r="H33" s="22" t="e">
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2249,7 +2225,7 @@
         <f>C5-C33</f>
         <v>0</v>
       </c>
-      <c r="D34" s="26" t="e">
+      <c r="D34" s="23" t="e">
         <f>100-D33</f>
         <v>#DIV/0!</v>
       </c>
@@ -2260,7 +2236,7 @@
         <f>G5-G33</f>
         <v>0</v>
       </c>
-      <c r="H34" s="26" t="e">
+      <c r="H34" s="23" t="e">
         <f>100-H33</f>
         <v>#DIV/0!</v>
       </c>
@@ -2317,587 +2293,587 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:15" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="52"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="47">
+      <c r="D3" s="33"/>
+      <c r="E3" s="43">
         <v>2000</v>
       </c>
-      <c r="F3" s="62"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="54"/>
+      <c r="F3" s="52"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="63"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="47">
+      <c r="D4" s="33"/>
+      <c r="E4" s="43">
         <v>1000</v>
       </c>
-      <c r="F4" s="62"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="56"/>
+      <c r="F4" s="52"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="34"/>
-      <c r="B5" s="32" t="s">
+      <c r="A5" s="31"/>
+      <c r="B5" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="33">
+      <c r="D5" s="44"/>
+      <c r="E5" s="30">
         <v>2000</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="N5" s="57" t="s">
+      <c r="F5" s="52"/>
+      <c r="N5" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="O5" s="47" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="34"/>
-      <c r="B6" s="32" t="s">
+      <c r="A6" s="31"/>
+      <c r="B6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="33">
+      <c r="D6" s="44"/>
+      <c r="E6" s="30">
         <v>1050</v>
       </c>
-      <c r="F6" s="62"/>
-      <c r="N6" s="28" t="s">
+      <c r="F6" s="52"/>
+      <c r="N6" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="28" t="s">
+      <c r="O6" s="25" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="34"/>
-      <c r="B7" s="32" t="s">
+      <c r="A7" s="31"/>
+      <c r="B7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="33">
+      <c r="D7" s="38"/>
+      <c r="E7" s="30">
         <v>645</v>
       </c>
-      <c r="F7" s="62"/>
+      <c r="F7" s="52"/>
       <c r="M7" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="29" t="s">
+      <c r="O7" s="26" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="32" t="s">
+      <c r="A8" s="31"/>
+      <c r="B8" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="33">
+      <c r="D8" s="38"/>
+      <c r="E8" s="30">
         <v>150</v>
       </c>
-      <c r="F8" s="62"/>
-      <c r="G8" s="61"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="51"/>
       <c r="M8" t="s">
         <v>28</v>
       </c>
-      <c r="N8" s="29" t="s">
+      <c r="N8" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="29" t="s">
+      <c r="O8" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="34"/>
-      <c r="B9" s="32" t="s">
+      <c r="A9" s="31"/>
+      <c r="B9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="33">
+      <c r="D9" s="38"/>
+      <c r="E9" s="30">
         <v>200</v>
       </c>
-      <c r="F9" s="62"/>
+      <c r="F9" s="52"/>
       <c r="M9" t="s">
         <v>29</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="N9" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="O9" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="32" t="s">
+      <c r="A10" s="31"/>
+      <c r="B10" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="33">
+      <c r="D10" s="38"/>
+      <c r="E10" s="30">
         <v>630</v>
       </c>
-      <c r="F10" s="62"/>
+      <c r="F10" s="52"/>
       <c r="M10" t="s">
         <v>30</v>
       </c>
-      <c r="N10" s="29" t="s">
+      <c r="N10" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="O10" s="28" t="s">
+      <c r="O10" s="25" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="34"/>
-      <c r="B11" s="37" t="s">
+      <c r="A11" s="31"/>
+      <c r="B11" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="38">
+      <c r="D11" s="45"/>
+      <c r="E11" s="35">
         <f>7500/12</f>
         <v>625</v>
       </c>
-      <c r="F11" s="62"/>
+      <c r="F11" s="52"/>
       <c r="M11" t="s">
         <v>31</v>
       </c>
-      <c r="N11" s="30" t="s">
+      <c r="N11" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="O11" s="29" t="s">
+      <c r="O11" s="26" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="39" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="40">
+      <c r="D12" s="46"/>
+      <c r="E12" s="37">
         <v>500</v>
       </c>
-      <c r="F12" s="62"/>
+      <c r="F12" s="52"/>
       <c r="M12" t="s">
         <v>32</v>
       </c>
-      <c r="O12" s="29" t="s">
+      <c r="O12" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="27"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="24"/>
       <c r="M13" t="s">
         <v>33</v>
       </c>
-      <c r="O13" s="29" t="s">
+      <c r="O13" s="26" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="34"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42"/>
       <c r="M14" t="s">
         <v>34</v>
       </c>
-      <c r="O14" s="29" t="s">
+      <c r="O14" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="34"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="40"/>
-      <c r="J15" s="31"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="37"/>
+      <c r="J15" s="28"/>
       <c r="M15" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="29" t="s">
+      <c r="O15" s="26" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="34"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="40"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="37"/>
       <c r="M16" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="29" t="s">
+      <c r="O16" s="26" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="34"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="40"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="37"/>
       <c r="M17" t="s">
         <v>37</v>
       </c>
-      <c r="O17" s="29" t="s">
+      <c r="O17" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="40"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="37"/>
       <c r="M18" t="s">
         <v>38</v>
       </c>
-      <c r="O18" s="29" t="s">
+      <c r="O18" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="34"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="40"/>
-      <c r="O19" s="29" t="s">
+      <c r="A19" s="31"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="37"/>
+      <c r="O19" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="34"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="40"/>
-      <c r="O20" s="42" t="s">
+      <c r="A20" s="31"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="37"/>
+      <c r="O20" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="34"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="40"/>
-      <c r="O21" s="29" t="s">
+      <c r="A21" s="31"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="37"/>
+      <c r="O21" s="26" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="40"/>
-      <c r="O22" s="29" t="s">
+      <c r="A22" s="31"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="37"/>
+      <c r="O22" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="34"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="40"/>
-      <c r="O23" s="29" t="s">
+      <c r="A23" s="31"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="37"/>
+      <c r="O23" s="26" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="34"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="40"/>
-      <c r="O24" s="29" t="s">
+      <c r="A24" s="31"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="37"/>
+      <c r="O24" s="26" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="34"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="40"/>
-      <c r="O25" s="30" t="s">
+      <c r="A25" s="31"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="37"/>
+      <c r="O25" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="40"/>
-      <c r="O26" s="28" t="s">
+      <c r="A26" s="31"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="37"/>
+      <c r="O26" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="34"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="40"/>
-      <c r="O27" s="29" t="s">
+      <c r="A27" s="31"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="37"/>
+      <c r="O27" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="34"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="40"/>
-      <c r="O28" s="30" t="s">
+      <c r="A28" s="31"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="37"/>
+      <c r="O28" s="27" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="34"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="40"/>
-      <c r="O29" s="28" t="s">
+      <c r="A29" s="31"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="37"/>
+      <c r="O29" s="25" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="34"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="40"/>
-      <c r="O30" s="29" t="s">
+      <c r="A30" s="31"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="37"/>
+      <c r="O30" s="26" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="34"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="40"/>
-      <c r="O31" s="29" t="s">
+      <c r="A31" s="31"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="37"/>
+      <c r="O31" s="26" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="34"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="40"/>
-      <c r="O32" s="42" t="s">
+      <c r="A32" s="31"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="37"/>
+      <c r="O32" s="27" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="34"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="40"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="37"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="34"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="40"/>
+      <c r="A34" s="31"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="37"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="34"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="40"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="37"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="34"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="40"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="37"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="40"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="37"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="34"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="40"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="37"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="34"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="40"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="37"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="34"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="40"/>
+      <c r="A40" s="31"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="37"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="34"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="40"/>
+      <c r="A41" s="31"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="37"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="34"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="40"/>
+      <c r="A42" s="31"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="37"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="34"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="40"/>
+      <c r="A43" s="31"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="37"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="34"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="40"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="37"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="34"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="40"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="37"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="34"/>
-      <c r="B46" s="39"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="40"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="37"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="34"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="40"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="37"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="34"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="40"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="37"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="34"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="40"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="37"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="34"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="40"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="37"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="34"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="40"/>
+      <c r="A51" s="31"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2905,12 +2881,10 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A3:E51">
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>#REF!=1</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:E51">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Income & Cost Spreadsheet.xlsx
+++ b/Income & Cost Spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usarmywestpoint-my.sharepoint.com/personal/nathan_davis2_westpoint_edu/Documents/Documents/MY OWN WEBSITE!!!/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1214" documentId="8_{6087132D-B281-4ECA-AD9E-C22E4686363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30A0D911-D74C-4AFD-B9F6-132A31FAD224}"/>
+  <xr:revisionPtr revIDLastSave="1279" documentId="8_{6087132D-B281-4ECA-AD9E-C22E4686363E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530F9CF3-3CBD-4329-866E-7532A6387022}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5016BA3E-3704-452A-B527-6130FB509E87}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
   <si>
     <t>Expenses</t>
   </si>
@@ -307,6 +307,15 @@
   <si>
     <t>Hello!</t>
   </si>
+  <si>
+    <t>DASHBOARD</t>
+  </si>
+  <si>
+    <t>NATE MONTHLY SCORE/INDEX</t>
+  </si>
+  <si>
+    <t>LEFTOVER PURCHASING POWER</t>
+  </si>
 </sst>
 </file>
 
@@ -315,7 +324,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,8 +405,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,8 +485,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -702,12 +753,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -855,6 +966,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1369,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE60D23-1EFA-4295-B03D-1823936C10C4}">
-  <dimension ref="B1:K34"/>
+  <dimension ref="B1:T56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -1383,7 +1517,7 @@
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="38.5546875" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="20.88671875" customWidth="1"/>
+    <col min="12" max="12" width="29.88671875" customWidth="1"/>
     <col min="13" max="13" width="19.44140625" customWidth="1"/>
     <col min="14" max="14" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.21875" customWidth="1"/>
@@ -1417,7 +1551,7 @@
     <col min="50" max="50" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:20" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B1" s="54" t="s">
         <v>73</v>
       </c>
@@ -1428,8 +1562,21 @@
       </c>
       <c r="G1" s="55"/>
       <c r="H1" s="56"/>
-    </row>
-    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+    </row>
+    <row r="2" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="57" t="s">
         <v>1</v>
       </c>
@@ -1440,11 +1587,19 @@
       </c>
       <c r="G2" s="58"/>
       <c r="H2" s="59"/>
-      <c r="J2" s="53" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+    </row>
+    <row r="3" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
@@ -1461,8 +1616,23 @@
         <v>0</v>
       </c>
       <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J3" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="66"/>
+      <c r="L3" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+    </row>
+    <row r="4" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>54</v>
       </c>
@@ -1479,14 +1649,24 @@
         <v>0</v>
       </c>
       <c r="H4" s="8"/>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J4" s="70">
+        <v>75</v>
+      </c>
+      <c r="K4" s="66"/>
+      <c r="L4" s="73">
+        <f>C34</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+    </row>
+    <row r="5" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,14 +1683,19 @@
         <v>0</v>
       </c>
       <c r="H5" s="8"/>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J5" s="71"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="66"/>
+    </row>
+    <row r="6" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="13" t="s">
         <v>0</v>
       </c>
@@ -1529,14 +1714,19 @@
       <c r="H6" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J6" s="72"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66"/>
+    </row>
+    <row r="7" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
@@ -1547,17 +1737,19 @@
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="16"/>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="66"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="17" t="s">
         <v>5</v>
       </c>
@@ -1580,17 +1772,19 @@
         <f t="shared" ref="H8:H17" si="1">G8/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9" s="17" t="s">
         <v>6</v>
       </c>
@@ -1613,17 +1807,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J9" s="66"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
@@ -1646,14 +1842,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J10" s="66"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B11" s="17" t="s">
         <v>8</v>
       </c>
@@ -1676,11 +1877,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J11" s="66"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="66"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="66"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="17" t="s">
         <v>9</v>
       </c>
@@ -1703,11 +1912,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="66"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="17" t="s">
         <v>10</v>
       </c>
@@ -1730,11 +1947,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J13" s="66"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="66"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
         <v>19</v>
       </c>
@@ -1757,11 +1982,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>11</v>
       </c>
@@ -1784,11 +2017,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B16" s="17" t="s">
         <v>61</v>
       </c>
@@ -1811,11 +2052,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J16" s="66"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="66"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+    </row>
+    <row r="17" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="17" t="s">
         <v>56</v>
       </c>
@@ -1838,11 +2087,19 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+    </row>
+    <row r="18" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
@@ -1859,11 +2116,20 @@
         <f>#REF!/$C$5*100</f>
         <v>#REF!</v>
       </c>
-      <c r="I18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="69"/>
+      <c r="J18" s="66"/>
+      <c r="K18" s="66"/>
+      <c r="L18" s="66"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="66"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="17" t="s">
         <v>13</v>
       </c>
@@ -1886,11 +2152,19 @@
         <f>G19/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I19">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="17" t="s">
         <v>14</v>
       </c>
@@ -1913,11 +2187,19 @@
         <f t="shared" ref="H20:H33" si="3">G20/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I20">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="17" t="s">
         <v>15</v>
       </c>
@@ -1940,8 +2222,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="17" t="s">
         <v>16</v>
       </c>
@@ -1964,8 +2257,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J22" s="66"/>
+      <c r="K22" s="66"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+    </row>
+    <row r="23" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="17" t="s">
         <v>55</v>
       </c>
@@ -1988,8 +2292,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J23" s="66"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+    </row>
+    <row r="24" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>17</v>
       </c>
@@ -2006,8 +2321,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J24" s="66"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="66"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="17" t="s">
         <v>18</v>
       </c>
@@ -2030,8 +2356,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J25" s="66"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="17" t="s">
         <v>21</v>
       </c>
@@ -2054,8 +2391,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+    </row>
+    <row r="27" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="17" t="s">
         <v>57</v>
       </c>
@@ -2078,8 +2426,19 @@
         <f>G27/$C$5*100</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+    </row>
+    <row r="28" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
         <v>22</v>
       </c>
@@ -2096,8 +2455,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="66"/>
+      <c r="P28" s="66"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="17" t="s">
         <v>23</v>
       </c>
@@ -2120,8 +2490,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="66"/>
+      <c r="S29" s="66"/>
+      <c r="T29" s="66"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B30" s="17" t="s">
         <v>24</v>
       </c>
@@ -2144,8 +2525,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="66"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="66"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="17" t="s">
         <v>25</v>
       </c>
@@ -2168,8 +2560,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="66"/>
+    </row>
+    <row r="32" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="17" t="s">
         <v>59</v>
       </c>
@@ -2192,8 +2595,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="33" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
+    </row>
+    <row r="33" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="9" t="s">
         <v>26</v>
       </c>
@@ -2216,8 +2630,19 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="34" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J33" s="66"/>
+      <c r="K33" s="66"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="66"/>
+      <c r="P33" s="66"/>
+      <c r="Q33" s="66"/>
+      <c r="R33" s="66"/>
+      <c r="S33" s="66"/>
+      <c r="T33" s="66"/>
+    </row>
+    <row r="34" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="11" t="s">
         <v>27</v>
       </c>
@@ -2240,13 +2665,147 @@
         <f>100-H33</f>
         <v>#DIV/0!</v>
       </c>
+      <c r="J34" s="66"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="66"/>
+      <c r="M34" s="66"/>
+      <c r="N34" s="66"/>
+      <c r="O34" s="66"/>
+      <c r="P34" s="66"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="66"/>
+      <c r="S34" s="66"/>
+      <c r="T34" s="66"/>
+    </row>
+    <row r="38" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J38" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <v>4</v>
+      </c>
+      <c r="J43" t="s">
+        <v>67</v>
+      </c>
+      <c r="K43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="K44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <v>6</v>
+      </c>
+      <c r="J45" t="s">
+        <v>71</v>
+      </c>
+      <c r="K45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <v>7</v>
+      </c>
+      <c r="J46" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="J1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
